--- a/URIARTE 630/Septiembre/EXPENSAS-Septiembre.xlsx
+++ b/URIARTE 630/Septiembre/EXPENSAS-Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\URIARTE 630\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF70083-472B-478B-A691-45D28943224B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD586E6-1BE9-4BA6-800D-8AAE4942A7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -233,9 +233,6 @@
     <t>Ingreso pago de expensas en termino</t>
   </si>
   <si>
-    <t>SERVISUR REGULACION DE SENSORES DE MOVIMIENTO</t>
-  </si>
-  <si>
     <t>Vto. 15/10</t>
   </si>
   <si>
@@ -243,6 +240,9 @@
   </si>
   <si>
     <t>ARTICULOS DE LIMPIEZA</t>
+  </si>
+  <si>
+    <t>AL LLEGAR LOS TRES MESES DE ABONO DE EXPENSAS NOS ENCONTRAMOS CON LAS FACULTADES DE DESCONECTAR A LAS UNIDADES FUNCIONALES DE LA RED DE EDESUR.</t>
   </si>
 </sst>
 </file>
@@ -256,7 +256,7 @@
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,15 +370,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +420,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1032,7 +1031,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1073,7 +1072,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -1186,6 +1184,29 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1201,12 +1222,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1216,26 +1231,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1604,56 +1602,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="17"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="54" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="53" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1661,354 +1659,360 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="109"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
+      <c r="F11" s="108"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="105">
+      <c r="B12" s="47"/>
+      <c r="C12" s="104">
         <v>71833</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="32">
-        <v>-606603.76407167991</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="48" t="s">
+      <c r="F12" s="31">
+        <v>-655462.99697167997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="134">
+      <c r="B13" s="47"/>
+      <c r="C13" s="104">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="56">
         <f>'prorrateo '!F10</f>
-        <v>484610.18209999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="55" t="s">
+        <v>354052.05059999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="46"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="24"/>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="77">
+      <c r="F14" s="76">
         <f>-C37 +C31</f>
-        <v>-593841.02500000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+        <v>-575207.57499999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="132">
+      <c r="B15" s="47"/>
+      <c r="C15" s="45">
         <v>140555</v>
       </c>
       <c r="D15" s="24"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="134">
-        <v>66605.490000000005</v>
+      <c r="B16" s="55"/>
+      <c r="C16" s="104">
+        <v>67972.039999999994</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="105">
+      <c r="B17" s="47"/>
+      <c r="C17" s="104">
         <v>42387.21</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="134">
+      <c r="B18" s="54"/>
+      <c r="C18" s="104">
         <v>212390.55</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="55" t="s">
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="105"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-    </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="49"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="107">
+      <c r="B19" s="47"/>
+      <c r="C19" s="104"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="106">
         <f>SUM(C12:C18)</f>
-        <v>538291.02500000002</v>
+        <v>539657.57499999995</v>
       </c>
       <c r="D20" s="10"/>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="35">
         <f>SUM(F12:F18)</f>
-        <v>-715834.60697167995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="51" t="s">
+        <v>-876618.52137167996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="108"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="107"/>
       <c r="D21" s="4"/>
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="133" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="45">
+        <v>35550</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="132">
-        <v>35550</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="46">
-        <v>20000</v>
-      </c>
+      <c r="F22" s="131"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="54"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="21"/>
       <c r="B24" s="22"/>
-      <c r="C24" s="47">
+      <c r="C24" s="46">
         <f>SUM(C21:C23)</f>
-        <v>55550</v>
+        <v>35550</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="30"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B25" s="27"/>
-      <c r="C25" s="80">
+      <c r="C25" s="79">
         <f>+C24+C20</f>
-        <v>593841.02500000002</v>
+        <v>575207.57499999995</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="42" t="s">
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="81"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="44"/>
+      <c r="C26" s="80"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="19"/>
-      <c r="C28" s="82"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="81"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
       <c r="B29" s="28"/>
-      <c r="C29" s="83">
+      <c r="C29" s="82">
         <v>0</v>
       </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="83">
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="82">
         <v>0</v>
       </c>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="84"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="110"/>
-      <c r="B32" s="110"/>
-      <c r="C32" s="83"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="83"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="109"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="82"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="28"/>
-      <c r="C33" s="83">
+      <c r="C33" s="82">
         <v>0</v>
       </c>
       <c r="F33" s="5"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="53">
+      <c r="B34" s="39"/>
+      <c r="C34" s="52">
         <f>SUM(C29:C33)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C35" s="83"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="82"/>
       <c r="F35" s="5"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="85">
+      <c r="C36" s="84">
         <f>C35+C25</f>
-        <v>593841.02500000002</v>
+        <v>575207.57499999995</v>
       </c>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="53">
+      <c r="B37" s="39"/>
+      <c r="C37" s="52">
         <f>+C25+C34</f>
-        <v>593841.02500000002</v>
+        <v>575207.57499999995</v>
       </c>
       <c r="E37" s="10"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="5"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="10"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D46" s="10"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="11"/>
       <c r="C58" s="13"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E22:F32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2026,72 +2030,76 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="0.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="0.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="120" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="128" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de SEPTIEMBRE</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="91"/>
-      <c r="G1" s="111" t="s">
+      <c r="F1" s="90"/>
+      <c r="G1" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="114">
-        <v>610434.56999999995</v>
-      </c>
-      <c r="M1" s="115"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="str">
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="126">
+        <f>Q1</f>
+        <v>575207.57499999995</v>
+      </c>
+      <c r="M1" s="127"/>
+      <c r="Q1">
+        <v>575207.57499999995</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="92" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 15/10</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="49" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="106">
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="105">
         <v>413723.43999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="94" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="93" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -2127,12 +2135,12 @@
       <c r="L3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="M3" s="95" t="s">
+      <c r="M3" s="94" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="94"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="93"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>41</v>
@@ -2147,7 +2155,7 @@
         <v>31</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="87">
+      <c r="H4" s="86">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2159,16 +2167,16 @@
       <c r="K4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="88" t="str">
+      <c r="L4" s="87" t="str">
         <f>A2</f>
         <v>Vto. 15/10</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="94" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="94">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="93">
         <v>1</v>
       </c>
       <c r="B5" s="7">
@@ -2177,29 +2185,27 @@
       <c r="C5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="51">
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>128164.01088799995</v>
-      </c>
-      <c r="F5" s="46">
-        <v>125000</v>
-      </c>
-      <c r="G5" s="89">
+        <v>131621.04750259191</v>
+      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="88">
         <f>E5-F5</f>
-        <v>3164.0108879999461</v>
-      </c>
-      <c r="H5" s="90">
+        <v>131621.04750259191</v>
+      </c>
+      <c r="H5" s="89">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>265.77691459199548</v>
+        <v>11056.167990217722</v>
       </c>
       <c r="I5" s="9">
         <v>0</v>
       </c>
       <c r="J5" s="23">
         <f>L$1*B5</f>
-        <v>128191.25969999998</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="K5" s="9">
         <f>K$2*D5</f>
@@ -2207,38 +2213,38 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>131621.04750259191</v>
-      </c>
-      <c r="M5" s="96">
+        <v>263470.80624280963</v>
+      </c>
+      <c r="M5" s="95">
         <f>L5+L5*4%</f>
-        <v>136885.88940269558</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="94">
+        <v>274009.638492522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="93">
         <v>2</v>
       </c>
       <c r="B6" s="7">
         <v>0.16</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="51">
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>101576</v>
-      </c>
-      <c r="F6" s="46">
+        <v>97669.531199999998</v>
+      </c>
+      <c r="F6" s="45">
         <f>E6</f>
-        <v>101576</v>
-      </c>
-      <c r="G6" s="89">
+        <v>97669.531199999998</v>
+      </c>
+      <c r="G6" s="88">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="90">
+      <c r="H6" s="89">
         <f t="shared" ref="H6:H9" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
         <v>0</v>
       </c>
@@ -2247,7 +2253,7 @@
       </c>
       <c r="J6" s="23">
         <f>L$1*B6</f>
-        <v>97669.531199999998</v>
+        <v>92033.212</v>
       </c>
       <c r="K6" s="9">
         <f>K$2*D6</f>
@@ -2255,55 +2261,55 @@
       </c>
       <c r="L6" s="9">
         <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
-        <v>97669.531199999998</v>
-      </c>
-      <c r="M6" s="96">
+        <v>92033.212</v>
+      </c>
+      <c r="M6" s="95">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>101576.312448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="94">
+        <v>95714.540479999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="93">
         <v>3</v>
       </c>
       <c r="B7" s="7">
         <v>0.21</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="52"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="23">
-        <v>128191.68740968405</v>
-      </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="89">
+        <v>267151.04885209748</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="88">
         <f t="shared" si="0"/>
-        <v>128191.68740968405</v>
-      </c>
-      <c r="H7" s="90">
+        <v>267151.04885209748</v>
+      </c>
+      <c r="H7" s="89">
         <f t="shared" si="1"/>
-        <v>10768.101742413461</v>
+        <v>22440.688103576191</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23">
         <f>L$1*B7</f>
-        <v>128191.25969999998</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>267151.04885209748</v>
-      </c>
-      <c r="M7" s="96">
+        <v>410385.32770567364</v>
+      </c>
+      <c r="M7" s="95">
         <f t="shared" si="3"/>
-        <v>277837.09080618137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="94">
+        <v>426800.7408139006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="93">
         <v>4</v>
       </c>
       <c r="B8" s="7">
@@ -2312,41 +2318,41 @@
       <c r="C8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="23">
-        <v>124715.18209999996</v>
-      </c>
-      <c r="F8" s="46">
+        <v>128191.25969999998</v>
+      </c>
+      <c r="F8" s="45">
         <f>E8</f>
-        <v>124715.18209999996</v>
-      </c>
-      <c r="G8" s="89">
+        <v>128191.25969999998</v>
+      </c>
+      <c r="G8" s="88">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="90">
+      <c r="H8" s="89">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="23">
         <f>L$1*B8</f>
-        <v>128191.25969999998</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>128191.25969999998</v>
-      </c>
-      <c r="M8" s="96">
+        <v>120793.59074999999</v>
+      </c>
+      <c r="M8" s="95">
         <f t="shared" si="3"/>
-        <v>133318.91008799998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="94">
+        <v>125625.33437999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="93">
         <v>5</v>
       </c>
       <c r="B9" s="7">
@@ -2355,135 +2361,135 @@
       <c r="C9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="23">
-        <v>133319</v>
-      </c>
-      <c r="F9" s="46">
+        <v>128191.25969999998</v>
+      </c>
+      <c r="F9" s="45">
         <f>E9</f>
-        <v>133319</v>
-      </c>
-      <c r="G9" s="89">
+        <v>128191.25969999998</v>
+      </c>
+      <c r="G9" s="88">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="89">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="23">
         <f>L$1*B9</f>
-        <v>128191.25969999998</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="2"/>
-        <v>128191.25969999998</v>
-      </c>
-      <c r="M9" s="96">
+        <v>120793.59074999999</v>
+      </c>
+      <c r="M9" s="95">
         <f t="shared" si="3"/>
-        <v>133318.91008799998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="97" t="s">
+        <v>125625.33437999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="98">
+      <c r="B10" s="97">
         <f>SUM(B5:B9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="100">
+      <c r="C10" s="98"/>
+      <c r="D10" s="99">
         <f t="shared" ref="D10:K10" si="4">SUM(D5:D6)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="100">
         <f>SUM(E5:E9)</f>
-        <v>615965.88039768394</v>
-      </c>
-      <c r="F10" s="101">
+        <v>752824.14695468929</v>
+      </c>
+      <c r="F10" s="100">
         <f>SUM(F5:F9)</f>
-        <v>484610.18209999998</v>
-      </c>
-      <c r="G10" s="101">
+        <v>354052.05059999996</v>
+      </c>
+      <c r="G10" s="100">
         <f t="shared" si="4"/>
-        <v>3164.0108879999461</v>
-      </c>
-      <c r="H10" s="101">
+        <v>131621.04750259191</v>
+      </c>
+      <c r="H10" s="100">
         <f t="shared" si="4"/>
-        <v>265.77691459199548</v>
-      </c>
-      <c r="I10" s="102">
+        <v>11056.167990217722</v>
+      </c>
+      <c r="I10" s="101">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="102">
         <f>SUM(J5:J9)</f>
-        <v>610434.56999999995</v>
-      </c>
-      <c r="K10" s="103">
+        <v>575207.57499999995</v>
+      </c>
+      <c r="K10" s="102">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="101">
+      <c r="L10" s="100">
         <f>SUM(L5:L9)</f>
-        <v>752824.14695468929</v>
-      </c>
-      <c r="M10" s="104">
+        <v>1007476.5274484833</v>
+      </c>
+      <c r="M10" s="103">
         <f>SUM(M5:M9)</f>
-        <v>782937.11283287697</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1047775.5885464227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="123" t="s">
+    <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="64"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="125" t="s">
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="63"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="64"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="63"/>
       <c r="R15" t="s">
         <v>39</v>
       </c>
@@ -2491,19 +2497,19 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C16" s="59"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C16" s="58"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="64"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="63"/>
       <c r="R16" t="s">
         <v>37</v>
       </c>
@@ -2511,21 +2517,21 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C17" s="61" t="s">
+    <row r="17" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C17" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64" t="s">
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="62"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="64"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="63"/>
       <c r="R17" t="s">
         <v>40</v>
       </c>
@@ -2533,17 +2539,17 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="64"/>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="63"/>
       <c r="R18" t="s">
         <v>38</v>
       </c>
@@ -2551,31 +2557,31 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C19" s="126" t="s">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C19" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="64"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C20" s="61"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="64"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="63"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C20" s="60"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="63"/>
       <c r="R20" t="s">
         <v>44</v>
       </c>
@@ -2583,1330 +2589,1307 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C21" s="61" t="s">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C21" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64" t="str">
+      <c r="D21" s="63"/>
+      <c r="E21" s="63" t="str">
         <f>C5</f>
         <v>TARQUIRINI SABRINA</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64" t="s">
+      <c r="F21" s="63"/>
+      <c r="G21" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="68"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="129" t="s">
+      <c r="H21" s="67"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="130"/>
-      <c r="L21" s="78"/>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C22" s="61" t="s">
+      <c r="K21" s="111"/>
+      <c r="L21" s="77"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C22" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="64">
+      <c r="E22" s="63">
         <f>A5</f>
         <v>1</v>
       </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="64"/>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C23" s="61"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="78"/>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C24" s="75" t="s">
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="63"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C23" s="60"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="77"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C24" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="74">
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="73">
         <f>L$1/5</f>
-        <v>122086.91399999999</v>
-      </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="64"/>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C25" s="76" t="s">
+        <v>115041.51499999998</v>
+      </c>
+      <c r="I24" s="61"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="63"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="74">
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="73">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="64"/>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C26" s="76" t="s">
+      <c r="I25" s="61"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="63"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C26" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="74">
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="73">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="64"/>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C27" s="76" t="s">
+      <c r="I26" s="61"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="63"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C27" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="74">
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="73">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I27" s="62"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="64"/>
-    </row>
-    <row r="28" spans="3:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="76" t="s">
+      <c r="I27" s="61"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="63"/>
+    </row>
+    <row r="28" spans="3:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="74">
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="73">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I28" s="62"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="64"/>
-    </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="64"/>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C30" s="76" t="s">
+      <c r="I28" s="61"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="63"/>
+    </row>
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="63"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C30" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="74">
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="73">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I30" s="62"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="64"/>
-    </row>
-    <row r="31" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="61"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="64"/>
-    </row>
-    <row r="32" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="116" t="s">
+      <c r="I30" s="61"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="63"/>
+    </row>
+    <row r="31" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="60"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="63"/>
+    </row>
+    <row r="32" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="118">
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="114">
         <f>SUM(H24:H31)</f>
-        <v>167453.2965</v>
-      </c>
-      <c r="I32" s="119"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="64"/>
-    </row>
-    <row r="35" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="123" t="s">
+        <v>160407.89749999999</v>
+      </c>
+      <c r="I32" s="115"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="63"/>
+    </row>
+    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="64"/>
-    </row>
-    <row r="37" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="125" t="s">
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="63"/>
+    </row>
+    <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="64"/>
-    </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="59"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64" t="s">
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="63"/>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="58"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="64"/>
-    </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="61" t="s">
+      <c r="I38" s="61"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="63"/>
+    </row>
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C39" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64" t="str">
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I39" s="62"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="64"/>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C40" s="65"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="64"/>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C41" s="126" t="s">
+      <c r="I39" s="61"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="63"/>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="64"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="63"/>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="128"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="64"/>
-    </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C42" s="61"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="64"/>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="61" t="s">
+      <c r="D41" s="121"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="121"/>
+      <c r="G41" s="121"/>
+      <c r="H41" s="121"/>
+      <c r="I41" s="122"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="63"/>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C42" s="60"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="63"/>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64" t="str">
+      <c r="D43" s="63"/>
+      <c r="E43" s="63" t="str">
         <f>C7</f>
         <v>LUCA BASUALDO</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64" t="s">
+      <c r="F43" s="63"/>
+      <c r="G43" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="62"/>
-      <c r="J43" s="129" t="s">
+      <c r="H43" s="67"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="130"/>
-      <c r="L43" s="78"/>
-    </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C44" s="61" t="s">
+      <c r="K43" s="111"/>
+      <c r="L43" s="77"/>
+    </row>
+    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="69" t="s">
+      <c r="D44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E44" s="64">
+      <c r="E44" s="63">
         <f>A7</f>
         <v>3</v>
       </c>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="62"/>
-      <c r="J44" s="61"/>
-      <c r="K44" s="62"/>
-      <c r="L44" s="64"/>
-    </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C45" s="61"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="131"/>
-      <c r="K45" s="130"/>
-      <c r="L45" s="78"/>
-    </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="61" t="s">
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="61"/>
+      <c r="L44" s="63"/>
+    </row>
+    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="60"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="110"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="77"/>
+    </row>
+    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="74">
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="73">
         <f>L$1/5</f>
-        <v>122086.91399999999</v>
-      </c>
-      <c r="I46" s="62"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="64"/>
-    </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="61"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="64"/>
-      <c r="H47" s="64"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="61"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="64"/>
-    </row>
-    <row r="48" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="61"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="70"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="64"/>
-    </row>
-    <row r="49" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="116" t="s">
+        <v>115041.51499999998</v>
+      </c>
+      <c r="I46" s="61"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="63"/>
+    </row>
+    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="60"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="63"/>
+    </row>
+    <row r="48" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="60"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="63"/>
+    </row>
+    <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="118">
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="113"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="114">
         <f>M6</f>
-        <v>101576.312448</v>
-      </c>
-      <c r="I49" s="119"/>
-      <c r="J49" s="72"/>
-      <c r="K49" s="73"/>
-      <c r="L49" s="64"/>
-    </row>
-    <row r="51" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="123" t="s">
+        <v>95714.540479999996</v>
+      </c>
+      <c r="I49" s="115"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="63"/>
+    </row>
+    <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="60"/>
-      <c r="L52" s="64"/>
-    </row>
-    <row r="53" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="125" t="s">
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="118"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="58"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="63"/>
+    </row>
+    <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-      <c r="F53" s="124"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="61"/>
-      <c r="K53" s="62"/>
-      <c r="L53" s="64"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C54" s="59"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="64" t="s">
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
+      <c r="I53" s="115"/>
+      <c r="J53" s="60"/>
+      <c r="K53" s="61"/>
+      <c r="L53" s="63"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C54" s="58"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I54" s="62"/>
-      <c r="J54" s="61"/>
-      <c r="K54" s="62"/>
-      <c r="L54" s="64"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C55" s="61" t="s">
+      <c r="I54" s="61"/>
+      <c r="J54" s="60"/>
+      <c r="K54" s="61"/>
+      <c r="L54" s="63"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C55" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64" t="str">
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I55" s="62"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="62"/>
-      <c r="L55" s="64"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C56" s="65"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="61"/>
-      <c r="K56" s="62"/>
-      <c r="L56" s="64"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C57" s="126" t="s">
+      <c r="I55" s="61"/>
+      <c r="J55" s="60"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="63"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="64"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="63"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="127"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="127"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="127"/>
-      <c r="I57" s="128"/>
-      <c r="J57" s="61"/>
-      <c r="K57" s="62"/>
-      <c r="L57" s="64"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C58" s="61"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="62"/>
-      <c r="J58" s="61"/>
-      <c r="K58" s="62"/>
-      <c r="L58" s="64"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C59" s="61" t="s">
+      <c r="D57" s="121"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
+      <c r="G57" s="121"/>
+      <c r="H57" s="121"/>
+      <c r="I57" s="122"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="63"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="60"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="60"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="63"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64" t="str">
+      <c r="D59" s="63"/>
+      <c r="E59" s="63" t="str">
         <f>C6</f>
         <v>CASTILLO JONATHAN</v>
       </c>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64" t="s">
+      <c r="F59" s="63"/>
+      <c r="G59" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="H59" s="68"/>
-      <c r="I59" s="62"/>
-      <c r="J59" s="129" t="s">
+      <c r="H59" s="67"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K59" s="130"/>
-      <c r="L59" s="78"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C60" s="61" t="s">
+      <c r="K59" s="111"/>
+      <c r="L59" s="77"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="69" t="s">
+      <c r="D60" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E60" s="64">
+      <c r="E60" s="63">
         <f>A6</f>
         <v>2</v>
       </c>
-      <c r="F60" s="64"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="64"/>
-      <c r="I60" s="62"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="64"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="61"/>
-      <c r="D61" s="64"/>
-      <c r="E61" s="64"/>
-      <c r="F61" s="64"/>
-      <c r="G61" s="64"/>
-      <c r="H61" s="64"/>
-      <c r="I61" s="62"/>
-      <c r="J61" s="131"/>
-      <c r="K61" s="130"/>
-      <c r="L61" s="78"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C62" s="61" t="s">
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="60"/>
+      <c r="K60" s="61"/>
+      <c r="L60" s="63"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="60"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="61"/>
+      <c r="J61" s="110"/>
+      <c r="K61" s="111"/>
+      <c r="L61" s="77"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="64"/>
-      <c r="F62" s="64"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="74">
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="73">
         <f>L$1/5</f>
-        <v>122086.91399999999</v>
-      </c>
-      <c r="I62" s="62"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="62"/>
-      <c r="L62" s="64"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C63" s="76" t="s">
+        <v>115041.51499999998</v>
+      </c>
+      <c r="I62" s="61"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="61"/>
+      <c r="L62" s="63"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="64"/>
-      <c r="F63" s="64"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="74">
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="73">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I63" s="62"/>
-      <c r="J63" s="61"/>
-      <c r="K63" s="62"/>
-      <c r="L63" s="64"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C64" s="76" t="s">
+      <c r="I63" s="61"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="61"/>
+      <c r="L63" s="63"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D64" s="64"/>
-      <c r="E64" s="64"/>
-      <c r="F64" s="64"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="74">
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="73">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I64" s="62"/>
-      <c r="J64" s="61"/>
-      <c r="K64" s="62"/>
-      <c r="L64" s="64"/>
-    </row>
-    <row r="65" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C65" s="76" t="s">
+      <c r="I64" s="61"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="61"/>
+      <c r="L64" s="63"/>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C65" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D65" s="64"/>
-      <c r="E65" s="64"/>
-      <c r="F65" s="64"/>
-      <c r="G65" s="64"/>
-      <c r="H65" s="74">
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="73">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I65" s="62"/>
-      <c r="J65" s="61"/>
-      <c r="K65" s="62"/>
-      <c r="L65" s="64"/>
-    </row>
-    <row r="66" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C66" s="76" t="s">
+      <c r="I65" s="61"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="61"/>
+      <c r="L65" s="63"/>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C66" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="64"/>
-      <c r="G66" s="64"/>
-      <c r="H66" s="74">
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="73">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I66" s="62"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="62"/>
-      <c r="L66" s="64"/>
-    </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="64"/>
-      <c r="E67" s="64"/>
-      <c r="F67" s="64"/>
-      <c r="G67" s="64"/>
-      <c r="H67" s="74"/>
-      <c r="I67" s="62"/>
-      <c r="J67" s="61"/>
-      <c r="K67" s="62"/>
-      <c r="L67" s="64"/>
-    </row>
-    <row r="68" spans="3:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="76" t="s">
+      <c r="I66" s="61"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="61"/>
+      <c r="L66" s="63"/>
+    </row>
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="61"/>
+      <c r="L67" s="63"/>
+    </row>
+    <row r="68" spans="3:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D68" s="64"/>
-      <c r="E68" s="64"/>
-      <c r="F68" s="64"/>
-      <c r="G68" s="64"/>
-      <c r="H68" s="74">
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
+      <c r="H68" s="73">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I68" s="62"/>
-      <c r="J68" s="61"/>
-      <c r="K68" s="62"/>
-      <c r="L68" s="64"/>
-    </row>
-    <row r="69" spans="3:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="61"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
-      <c r="I69" s="62"/>
-      <c r="J69" s="61"/>
-      <c r="K69" s="62"/>
-      <c r="L69" s="64"/>
-    </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="61"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="62"/>
-      <c r="J70" s="61"/>
-      <c r="K70" s="62"/>
-      <c r="L70" s="64"/>
-    </row>
-    <row r="71" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="61"/>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64"/>
-      <c r="F71" s="64"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="64"/>
-      <c r="I71" s="62"/>
-      <c r="J71" s="70"/>
-      <c r="K71" s="71"/>
-      <c r="L71" s="64"/>
-    </row>
-    <row r="72" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="116" t="s">
+      <c r="I68" s="61"/>
+      <c r="J68" s="60"/>
+      <c r="K68" s="61"/>
+      <c r="L68" s="63"/>
+    </row>
+    <row r="69" spans="3:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="60"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="61"/>
+      <c r="L69" s="63"/>
+    </row>
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="60"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="61"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="61"/>
+      <c r="L70" s="63"/>
+    </row>
+    <row r="71" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="60"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="61"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="63"/>
+    </row>
+    <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="118">
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="113"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="114">
         <f>SUM(H62:H71)</f>
-        <v>167453.2965</v>
-      </c>
-      <c r="I72" s="119"/>
-      <c r="J72" s="72"/>
-      <c r="K72" s="73"/>
-      <c r="L72" s="64"/>
-    </row>
-    <row r="75" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="123" t="s">
+        <v>160407.89749999999</v>
+      </c>
+      <c r="I72" s="115"/>
+      <c r="J72" s="71"/>
+      <c r="K72" s="72"/>
+      <c r="L72" s="63"/>
+    </row>
+    <row r="75" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="124"/>
-      <c r="E76" s="124"/>
-      <c r="F76" s="124"/>
-      <c r="G76" s="124"/>
-      <c r="H76" s="124"/>
-      <c r="I76" s="119"/>
-      <c r="J76" s="59"/>
-      <c r="K76" s="60"/>
-      <c r="L76" s="64"/>
-    </row>
-    <row r="77" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="125" t="s">
+      <c r="D76" s="118"/>
+      <c r="E76" s="118"/>
+      <c r="F76" s="118"/>
+      <c r="G76" s="118"/>
+      <c r="H76" s="118"/>
+      <c r="I76" s="115"/>
+      <c r="J76" s="58"/>
+      <c r="K76" s="59"/>
+      <c r="L76" s="63"/>
+    </row>
+    <row r="77" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="124"/>
-      <c r="E77" s="124"/>
-      <c r="F77" s="124"/>
-      <c r="G77" s="124"/>
-      <c r="H77" s="124"/>
-      <c r="I77" s="119"/>
-      <c r="J77" s="61"/>
-      <c r="K77" s="62"/>
-      <c r="L77" s="64"/>
-    </row>
-    <row r="78" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C78" s="59"/>
-      <c r="D78" s="63"/>
-      <c r="E78" s="63"/>
-      <c r="F78" s="63"/>
-      <c r="G78" s="64"/>
-      <c r="H78" s="64" t="s">
+      <c r="D77" s="118"/>
+      <c r="E77" s="118"/>
+      <c r="F77" s="118"/>
+      <c r="G77" s="118"/>
+      <c r="H77" s="118"/>
+      <c r="I77" s="115"/>
+      <c r="J77" s="60"/>
+      <c r="K77" s="61"/>
+      <c r="L77" s="63"/>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C78" s="58"/>
+      <c r="D78" s="62"/>
+      <c r="E78" s="62"/>
+      <c r="F78" s="62"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I78" s="62"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="62"/>
-      <c r="L78" s="64"/>
-    </row>
-    <row r="79" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C79" s="61" t="s">
+      <c r="I78" s="61"/>
+      <c r="J78" s="60"/>
+      <c r="K78" s="61"/>
+      <c r="L78" s="63"/>
+    </row>
+    <row r="79" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C79" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="64"/>
-      <c r="H79" s="64" t="str">
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I79" s="62"/>
-      <c r="J79" s="61"/>
-      <c r="K79" s="62"/>
-      <c r="L79" s="64"/>
-    </row>
-    <row r="80" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C80" s="65"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="67"/>
-      <c r="J80" s="61"/>
-      <c r="K80" s="62"/>
-      <c r="L80" s="64"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C81" s="126" t="s">
+      <c r="I79" s="61"/>
+      <c r="J79" s="60"/>
+      <c r="K79" s="61"/>
+      <c r="L79" s="63"/>
+    </row>
+    <row r="80" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C80" s="64"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="60"/>
+      <c r="K80" s="61"/>
+      <c r="L80" s="63"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="D81" s="127"/>
-      <c r="E81" s="127"/>
-      <c r="F81" s="127"/>
-      <c r="G81" s="127"/>
-      <c r="H81" s="127"/>
-      <c r="I81" s="128"/>
-      <c r="J81" s="61"/>
-      <c r="K81" s="62"/>
-      <c r="L81" s="64"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C82" s="61"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="62"/>
-      <c r="J82" s="61"/>
-      <c r="K82" s="62"/>
-      <c r="L82" s="64"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C83" s="61" t="s">
+      <c r="D81" s="121"/>
+      <c r="E81" s="121"/>
+      <c r="F81" s="121"/>
+      <c r="G81" s="121"/>
+      <c r="H81" s="121"/>
+      <c r="I81" s="122"/>
+      <c r="J81" s="60"/>
+      <c r="K81" s="61"/>
+      <c r="L81" s="63"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="60"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="61"/>
+      <c r="J82" s="60"/>
+      <c r="K82" s="61"/>
+      <c r="L82" s="63"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="64" t="str">
+      <c r="D83" s="63"/>
+      <c r="E83" s="63" t="str">
         <f>C8</f>
         <v xml:space="preserve">JOHANA </v>
       </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64" t="s">
+      <c r="F83" s="63"/>
+      <c r="G83" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="H83" s="68"/>
-      <c r="I83" s="62"/>
-      <c r="J83" s="129" t="s">
+      <c r="H83" s="67"/>
+      <c r="I83" s="61"/>
+      <c r="J83" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K83" s="130"/>
-      <c r="L83" s="78"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C84" s="61" t="s">
+      <c r="K83" s="111"/>
+      <c r="L83" s="77"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D84" s="69" t="s">
+      <c r="D84" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E84" s="64">
+      <c r="E84" s="63">
         <f>A8</f>
         <v>4</v>
       </c>
-      <c r="F84" s="64"/>
-      <c r="G84" s="64"/>
-      <c r="H84" s="64"/>
-      <c r="I84" s="62"/>
-      <c r="J84" s="61"/>
-      <c r="K84" s="62"/>
-      <c r="L84" s="64"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C85" s="61"/>
-      <c r="D85" s="64"/>
-      <c r="E85" s="64"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="64"/>
-      <c r="H85" s="64"/>
-      <c r="I85" s="62"/>
-      <c r="J85" s="131"/>
-      <c r="K85" s="130"/>
-      <c r="L85" s="78"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C86" s="61" t="s">
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="61"/>
+      <c r="J84" s="60"/>
+      <c r="K84" s="61"/>
+      <c r="L84" s="63"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="60"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="61"/>
+      <c r="J85" s="110"/>
+      <c r="K85" s="111"/>
+      <c r="L85" s="77"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="D86" s="64"/>
-      <c r="E86" s="64"/>
-      <c r="F86" s="64"/>
-      <c r="G86" s="64"/>
-      <c r="H86" s="74">
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="73">
         <f>L$1/5</f>
-        <v>122086.91399999999</v>
-      </c>
-      <c r="I86" s="62"/>
-      <c r="J86" s="61"/>
-      <c r="K86" s="62"/>
-      <c r="L86" s="64"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C87" s="76" t="s">
+        <v>115041.51499999998</v>
+      </c>
+      <c r="I86" s="61"/>
+      <c r="J86" s="60"/>
+      <c r="K86" s="61"/>
+      <c r="L86" s="63"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="74">
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="73">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I87" s="62"/>
-      <c r="J87" s="61"/>
-      <c r="K87" s="62"/>
-      <c r="L87" s="64"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C88" s="76" t="s">
+      <c r="I87" s="61"/>
+      <c r="J87" s="60"/>
+      <c r="K87" s="61"/>
+      <c r="L87" s="63"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
-      <c r="F88" s="64"/>
-      <c r="G88" s="64"/>
-      <c r="H88" s="74">
+      <c r="D88" s="63"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="73">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I88" s="62"/>
-      <c r="J88" s="61"/>
-      <c r="K88" s="62"/>
-      <c r="L88" s="64"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C89" s="76" t="s">
+      <c r="I88" s="61"/>
+      <c r="J88" s="60"/>
+      <c r="K88" s="61"/>
+      <c r="L88" s="63"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64"/>
-      <c r="F89" s="64"/>
-      <c r="G89" s="64"/>
-      <c r="H89" s="74">
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="73">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I89" s="62"/>
-      <c r="J89" s="61"/>
-      <c r="K89" s="62"/>
-      <c r="L89" s="64"/>
-    </row>
-    <row r="90" spans="3:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="76" t="s">
+      <c r="I89" s="61"/>
+      <c r="J89" s="60"/>
+      <c r="K89" s="61"/>
+      <c r="L89" s="63"/>
+    </row>
+    <row r="90" spans="3:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64"/>
-      <c r="F90" s="64"/>
-      <c r="G90" s="64"/>
-      <c r="H90" s="74">
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="73">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I90" s="62"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="62"/>
-      <c r="L90" s="64"/>
-    </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D91" s="64"/>
-      <c r="E91" s="64"/>
-      <c r="F91" s="64"/>
-      <c r="G91" s="64"/>
-      <c r="H91" s="74"/>
-      <c r="I91" s="62"/>
-      <c r="J91" s="61"/>
-      <c r="K91" s="62"/>
-      <c r="L91" s="64"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C92" s="76" t="s">
+      <c r="I90" s="61"/>
+      <c r="J90" s="60"/>
+      <c r="K90" s="61"/>
+      <c r="L90" s="63"/>
+    </row>
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="73"/>
+      <c r="I91" s="61"/>
+      <c r="J91" s="60"/>
+      <c r="K91" s="61"/>
+      <c r="L91" s="63"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D92" s="64"/>
-      <c r="E92" s="64"/>
-      <c r="F92" s="64"/>
-      <c r="G92" s="64"/>
-      <c r="H92" s="74">
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="73">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I92" s="62"/>
-      <c r="J92" s="70"/>
-      <c r="K92" s="71"/>
-      <c r="L92" s="64"/>
-    </row>
-    <row r="93" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D93" s="64"/>
-      <c r="E93" s="64"/>
-      <c r="F93" s="64"/>
-      <c r="G93" s="64"/>
-      <c r="H93" s="64"/>
-      <c r="I93" s="62"/>
-      <c r="J93" s="61"/>
-      <c r="K93" s="62"/>
-      <c r="L93" s="64"/>
-    </row>
-    <row r="94" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="116" t="s">
+      <c r="I92" s="61"/>
+      <c r="J92" s="69"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="63"/>
+    </row>
+    <row r="93" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="63"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="61"/>
+      <c r="J93" s="60"/>
+      <c r="K93" s="61"/>
+      <c r="L93" s="63"/>
+    </row>
+    <row r="94" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D94" s="117"/>
-      <c r="E94" s="117"/>
-      <c r="F94" s="117"/>
-      <c r="G94" s="117"/>
-      <c r="H94" s="118">
+      <c r="D94" s="113"/>
+      <c r="E94" s="113"/>
+      <c r="F94" s="113"/>
+      <c r="G94" s="113"/>
+      <c r="H94" s="114">
         <f>SUM(H86:H93)</f>
-        <v>167453.2965</v>
-      </c>
-      <c r="I94" s="119"/>
-      <c r="J94" s="72"/>
-      <c r="K94" s="73"/>
-      <c r="L94" s="64"/>
-    </row>
-    <row r="97" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="98" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="123" t="s">
+        <v>160407.89749999999</v>
+      </c>
+      <c r="I94" s="115"/>
+      <c r="J94" s="71"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="63"/>
+    </row>
+    <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="119"/>
-      <c r="J98" s="59"/>
-      <c r="K98" s="60"/>
-      <c r="L98" s="64"/>
-    </row>
-    <row r="99" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="125" t="s">
+      <c r="D98" s="118"/>
+      <c r="E98" s="118"/>
+      <c r="F98" s="118"/>
+      <c r="G98" s="118"/>
+      <c r="H98" s="118"/>
+      <c r="I98" s="115"/>
+      <c r="J98" s="58"/>
+      <c r="K98" s="59"/>
+      <c r="L98" s="63"/>
+    </row>
+    <row r="99" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="119"/>
-      <c r="J99" s="61"/>
-      <c r="K99" s="62"/>
-      <c r="L99" s="64"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C100" s="59"/>
-      <c r="D100" s="63"/>
-      <c r="E100" s="63"/>
-      <c r="F100" s="63"/>
-      <c r="G100" s="64"/>
-      <c r="H100" s="64" t="s">
+      <c r="D99" s="118"/>
+      <c r="E99" s="118"/>
+      <c r="F99" s="118"/>
+      <c r="G99" s="118"/>
+      <c r="H99" s="118"/>
+      <c r="I99" s="115"/>
+      <c r="J99" s="60"/>
+      <c r="K99" s="61"/>
+      <c r="L99" s="63"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C100" s="58"/>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="62"/>
+      <c r="G100" s="63"/>
+      <c r="H100" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I100" s="62"/>
-      <c r="J100" s="61"/>
-      <c r="K100" s="62"/>
-      <c r="L100" s="64"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C101" s="61" t="s">
+      <c r="I100" s="61"/>
+      <c r="J100" s="60"/>
+      <c r="K100" s="61"/>
+      <c r="L100" s="63"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C101" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D101" s="64"/>
-      <c r="E101" s="64"/>
-      <c r="F101" s="64"/>
-      <c r="G101" s="64"/>
-      <c r="H101" s="64" t="str">
+      <c r="D101" s="63"/>
+      <c r="E101" s="63"/>
+      <c r="F101" s="63"/>
+      <c r="G101" s="63"/>
+      <c r="H101" s="63" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I101" s="62"/>
-      <c r="J101" s="61"/>
-      <c r="K101" s="62"/>
-      <c r="L101" s="64"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C102" s="65"/>
-      <c r="D102" s="66"/>
-      <c r="E102" s="66"/>
-      <c r="F102" s="66"/>
-      <c r="G102" s="66"/>
-      <c r="H102" s="66"/>
-      <c r="I102" s="67"/>
-      <c r="J102" s="61"/>
-      <c r="K102" s="62"/>
-      <c r="L102" s="64"/>
-    </row>
-    <row r="103" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C103" s="126" t="s">
+      <c r="I101" s="61"/>
+      <c r="J101" s="60"/>
+      <c r="K101" s="61"/>
+      <c r="L101" s="63"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C102" s="64"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="65"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="66"/>
+      <c r="J102" s="60"/>
+      <c r="K102" s="61"/>
+      <c r="L102" s="63"/>
+    </row>
+    <row r="103" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C103" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="D103" s="127"/>
-      <c r="E103" s="127"/>
-      <c r="F103" s="127"/>
-      <c r="G103" s="127"/>
-      <c r="H103" s="127"/>
-      <c r="I103" s="128"/>
-      <c r="J103" s="61"/>
-      <c r="K103" s="62"/>
-      <c r="L103" s="64"/>
-    </row>
-    <row r="104" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C104" s="61"/>
-      <c r="D104" s="64"/>
-      <c r="E104" s="64"/>
-      <c r="F104" s="64"/>
-      <c r="G104" s="64"/>
-      <c r="H104" s="64"/>
-      <c r="I104" s="62"/>
-      <c r="J104" s="61"/>
-      <c r="K104" s="62"/>
-      <c r="L104" s="64"/>
-    </row>
-    <row r="105" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C105" s="61" t="s">
+      <c r="D103" s="121"/>
+      <c r="E103" s="121"/>
+      <c r="F103" s="121"/>
+      <c r="G103" s="121"/>
+      <c r="H103" s="121"/>
+      <c r="I103" s="122"/>
+      <c r="J103" s="60"/>
+      <c r="K103" s="61"/>
+      <c r="L103" s="63"/>
+    </row>
+    <row r="104" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C104" s="60"/>
+      <c r="D104" s="63"/>
+      <c r="E104" s="63"/>
+      <c r="F104" s="63"/>
+      <c r="G104" s="63"/>
+      <c r="H104" s="63"/>
+      <c r="I104" s="61"/>
+      <c r="J104" s="60"/>
+      <c r="K104" s="61"/>
+      <c r="L104" s="63"/>
+    </row>
+    <row r="105" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C105" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D105" s="64"/>
-      <c r="E105" s="64" t="str">
+      <c r="D105" s="63"/>
+      <c r="E105" s="63" t="str">
         <f>C9</f>
         <v xml:space="preserve">VARLAS GUILLERMO </v>
       </c>
-      <c r="F105" s="64"/>
-      <c r="G105" s="64" t="s">
+      <c r="F105" s="63"/>
+      <c r="G105" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="H105" s="68"/>
-      <c r="I105" s="62"/>
-      <c r="J105" s="129" t="s">
+      <c r="H105" s="67"/>
+      <c r="I105" s="61"/>
+      <c r="J105" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K105" s="130"/>
-      <c r="L105" s="78"/>
-    </row>
-    <row r="106" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C106" s="61" t="s">
+      <c r="K105" s="111"/>
+      <c r="L105" s="77"/>
+    </row>
+    <row r="106" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C106" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D106" s="69" t="s">
+      <c r="D106" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="64">
+      <c r="E106" s="63">
         <v>5</v>
       </c>
-      <c r="F106" s="64"/>
-      <c r="G106" s="64"/>
-      <c r="H106" s="64"/>
-      <c r="I106" s="62"/>
-      <c r="J106" s="61"/>
-      <c r="K106" s="62"/>
-      <c r="L106" s="64"/>
-    </row>
-    <row r="107" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C107" s="61"/>
-      <c r="D107" s="64"/>
-      <c r="E107" s="64"/>
-      <c r="F107" s="64"/>
-      <c r="G107" s="64"/>
-      <c r="H107" s="64"/>
-      <c r="I107" s="62"/>
-      <c r="J107" s="131"/>
-      <c r="K107" s="130"/>
-      <c r="L107" s="78"/>
-    </row>
-    <row r="108" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C108" s="61" t="s">
+      <c r="F106" s="63"/>
+      <c r="G106" s="63"/>
+      <c r="H106" s="63"/>
+      <c r="I106" s="61"/>
+      <c r="J106" s="60"/>
+      <c r="K106" s="61"/>
+      <c r="L106" s="63"/>
+    </row>
+    <row r="107" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C107" s="60"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="63"/>
+      <c r="F107" s="63"/>
+      <c r="G107" s="63"/>
+      <c r="H107" s="63"/>
+      <c r="I107" s="61"/>
+      <c r="J107" s="110"/>
+      <c r="K107" s="111"/>
+      <c r="L107" s="77"/>
+    </row>
+    <row r="108" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C108" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="D108" s="64"/>
-      <c r="E108" s="64"/>
-      <c r="F108" s="64"/>
-      <c r="G108" s="64"/>
-      <c r="H108" s="74">
+      <c r="D108" s="63"/>
+      <c r="E108" s="63"/>
+      <c r="F108" s="63"/>
+      <c r="G108" s="63"/>
+      <c r="H108" s="73">
         <f>L$1/5</f>
-        <v>122086.91399999999</v>
-      </c>
-      <c r="I108" s="62"/>
-      <c r="J108" s="61"/>
-      <c r="K108" s="62"/>
-      <c r="L108" s="64"/>
-    </row>
-    <row r="109" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C109" s="76" t="s">
+        <v>115041.51499999998</v>
+      </c>
+      <c r="I108" s="61"/>
+      <c r="J108" s="60"/>
+      <c r="K108" s="61"/>
+      <c r="L108" s="63"/>
+    </row>
+    <row r="109" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C109" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="64"/>
-      <c r="E109" s="64"/>
-      <c r="F109" s="64"/>
-      <c r="G109" s="64"/>
-      <c r="H109" s="74">
+      <c r="D109" s="63"/>
+      <c r="E109" s="63"/>
+      <c r="F109" s="63"/>
+      <c r="G109" s="63"/>
+      <c r="H109" s="73">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I109" s="62"/>
-      <c r="J109" s="61"/>
-      <c r="K109" s="62"/>
-      <c r="L109" s="64"/>
-    </row>
-    <row r="110" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C110" s="76" t="s">
+      <c r="I109" s="61"/>
+      <c r="J109" s="60"/>
+      <c r="K109" s="61"/>
+      <c r="L109" s="63"/>
+    </row>
+    <row r="110" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C110" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D110" s="64"/>
-      <c r="E110" s="64"/>
-      <c r="F110" s="64"/>
-      <c r="G110" s="64"/>
-      <c r="H110" s="74">
+      <c r="D110" s="63"/>
+      <c r="E110" s="63"/>
+      <c r="F110" s="63"/>
+      <c r="G110" s="63"/>
+      <c r="H110" s="73">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I110" s="62"/>
-      <c r="J110" s="61"/>
-      <c r="K110" s="62"/>
-      <c r="L110" s="64"/>
-    </row>
-    <row r="111" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C111" s="76" t="s">
+      <c r="I110" s="61"/>
+      <c r="J110" s="60"/>
+      <c r="K110" s="61"/>
+      <c r="L110" s="63"/>
+    </row>
+    <row r="111" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C111" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D111" s="64"/>
-      <c r="E111" s="64"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="74">
+      <c r="D111" s="63"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="73">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I111" s="62"/>
-      <c r="J111" s="61"/>
-      <c r="K111" s="62"/>
-      <c r="L111" s="64"/>
-    </row>
-    <row r="112" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C112" s="76" t="s">
+      <c r="I111" s="61"/>
+      <c r="J111" s="60"/>
+      <c r="K111" s="61"/>
+      <c r="L111" s="63"/>
+    </row>
+    <row r="112" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C112" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="74">
+      <c r="D112" s="63"/>
+      <c r="E112" s="63"/>
+      <c r="F112" s="63"/>
+      <c r="G112" s="63"/>
+      <c r="H112" s="73">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I112" s="62"/>
-      <c r="J112" s="61"/>
-      <c r="K112" s="62"/>
-      <c r="L112" s="64"/>
-    </row>
-    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D113" s="64"/>
-      <c r="E113" s="64"/>
-      <c r="F113" s="64"/>
-      <c r="G113" s="64"/>
-      <c r="H113" s="74"/>
-      <c r="I113" s="62"/>
-      <c r="J113" s="61"/>
-      <c r="K113" s="62"/>
-      <c r="L113" s="64"/>
-    </row>
-    <row r="114" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C114" s="76" t="s">
+      <c r="I112" s="61"/>
+      <c r="J112" s="60"/>
+      <c r="K112" s="61"/>
+      <c r="L112" s="63"/>
+    </row>
+    <row r="113" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D113" s="63"/>
+      <c r="E113" s="63"/>
+      <c r="F113" s="63"/>
+      <c r="G113" s="63"/>
+      <c r="H113" s="73"/>
+      <c r="I113" s="61"/>
+      <c r="J113" s="60"/>
+      <c r="K113" s="61"/>
+      <c r="L113" s="63"/>
+    </row>
+    <row r="114" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C114" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D114" s="64"/>
-      <c r="E114" s="64"/>
-      <c r="F114" s="64"/>
-      <c r="G114" s="64"/>
-      <c r="H114" s="74">
+      <c r="D114" s="63"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="63"/>
+      <c r="G114" s="63"/>
+      <c r="H114" s="73">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I114" s="62"/>
-      <c r="J114" s="70"/>
-      <c r="K114" s="71"/>
-      <c r="L114" s="64"/>
-    </row>
-    <row r="115" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D115" s="64"/>
-      <c r="E115" s="64"/>
-      <c r="F115" s="64"/>
-      <c r="G115" s="64"/>
-      <c r="H115" s="64"/>
-      <c r="I115" s="62"/>
-      <c r="J115" s="61"/>
-      <c r="K115" s="62"/>
-      <c r="L115" s="64"/>
-    </row>
-    <row r="116" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="116" t="s">
+      <c r="I114" s="61"/>
+      <c r="J114" s="69"/>
+      <c r="K114" s="70"/>
+      <c r="L114" s="63"/>
+    </row>
+    <row r="115" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D115" s="63"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="63"/>
+      <c r="G115" s="63"/>
+      <c r="H115" s="63"/>
+      <c r="I115" s="61"/>
+      <c r="J115" s="60"/>
+      <c r="K115" s="61"/>
+      <c r="L115" s="63"/>
+    </row>
+    <row r="116" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D116" s="117"/>
-      <c r="E116" s="117"/>
-      <c r="F116" s="117"/>
-      <c r="G116" s="117"/>
-      <c r="H116" s="118">
+      <c r="D116" s="113"/>
+      <c r="E116" s="113"/>
+      <c r="F116" s="113"/>
+      <c r="G116" s="113"/>
+      <c r="H116" s="114">
         <f>SUM(H108:H115)</f>
-        <v>167453.2965</v>
-      </c>
-      <c r="I116" s="119"/>
-      <c r="J116" s="72"/>
-      <c r="K116" s="73"/>
-      <c r="L116" s="64"/>
+        <v>160407.89749999999</v>
+      </c>
+      <c r="I116" s="115"/>
+      <c r="J116" s="71"/>
+      <c r="K116" s="72"/>
+      <c r="L116" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3923,6 +3906,29 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
